--- a/lab2/31.xlsx
+++ b/lab2/31.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/magdalenasmietana/Documents/Fizyka/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/magdalenasmietana/Documents/Fizyka/Fizyka-Lab/lab2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B42FD97-E8AD-6D49-A954-B0A7DC7CE3A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AE37496-DEDA-D149-8912-F58B65D92A22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="16760" xr2:uid="{9BA97022-0ECA-A347-BDBE-540DC07422D8}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{9BA97022-0ECA-A347-BDBE-540DC07422D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Cylindryczny" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="20">
   <si>
     <t>L.p.</t>
   </si>
@@ -91,11 +91,20 @@
   <si>
     <t>[m]</t>
   </si>
+  <si>
+    <t>x*[m]</t>
+  </si>
+  <si>
+    <t>u( E ) [V/m]</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="167" formatCode="0.0"/>
+  </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -158,7 +167,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -166,6 +175,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2791,14 +2801,8 @@
         <f>AVERAGE(B2:B3) / 1000</f>
         <v>1.0500000000000001E-2</v>
       </c>
-      <c r="K2" s="1">
-        <f>(C3-C2)/((B3-B2)/1000)</f>
-        <v>64.285714285714278</v>
-      </c>
-      <c r="L2" s="1">
-        <f>-B15/(J2*LN(B17/B16))</f>
-        <v>-900.02725588648184</v>
-      </c>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3">
@@ -2832,14 +2836,8 @@
         <f t="shared" ref="J3:J10" si="3">AVERAGE(B3:B4) / 1000</f>
         <v>1.7500000000000002E-2</v>
       </c>
-      <c r="K3" s="1">
-        <f t="shared" ref="K3:K10" si="4">(C4-C3)/((B4-B3)/1000)</f>
-        <v>74.28571428571432</v>
-      </c>
-      <c r="L3" s="1">
-        <f t="shared" ref="L3:L10" si="5">$B$15/($B$13 / 1000)</f>
-        <v>133.06666666666669</v>
-      </c>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4">
@@ -2873,14 +2871,8 @@
         <f t="shared" si="3"/>
         <v>2.4500000000000001E-2</v>
       </c>
-      <c r="K4" s="1">
-        <f t="shared" si="4"/>
-        <v>65.714285714285708</v>
-      </c>
-      <c r="L4" s="1">
-        <f t="shared" si="5"/>
-        <v>133.06666666666669</v>
-      </c>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5">
@@ -2914,14 +2906,8 @@
         <f t="shared" si="3"/>
         <v>3.15E-2</v>
       </c>
-      <c r="K5" s="1">
-        <f t="shared" si="4"/>
-        <v>78.571428571428541</v>
-      </c>
-      <c r="L5" s="1">
-        <f t="shared" si="5"/>
-        <v>133.06666666666669</v>
-      </c>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6">
@@ -2955,14 +2941,8 @@
         <f t="shared" si="3"/>
         <v>3.85E-2</v>
       </c>
-      <c r="K6" s="1">
-        <f t="shared" si="4"/>
-        <v>98.571428571428555</v>
-      </c>
-      <c r="L6" s="1">
-        <f t="shared" si="5"/>
-        <v>133.06666666666669</v>
-      </c>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7">
@@ -2996,14 +2976,8 @@
         <f t="shared" si="3"/>
         <v>4.5499999999999999E-2</v>
       </c>
-      <c r="K7" s="1">
-        <f t="shared" si="4"/>
-        <v>80.000000000000071</v>
-      </c>
-      <c r="L7" s="1">
-        <f t="shared" si="5"/>
-        <v>133.06666666666669</v>
-      </c>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8">
@@ -3037,14 +3011,8 @@
         <f t="shared" si="3"/>
         <v>5.2499999999999998E-2</v>
       </c>
-      <c r="K8" s="1">
-        <f t="shared" si="4"/>
-        <v>109.99999999999994</v>
-      </c>
-      <c r="L8" s="1">
-        <f t="shared" si="5"/>
-        <v>133.06666666666669</v>
-      </c>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9">
@@ -3078,14 +3046,8 @@
         <f t="shared" si="3"/>
         <v>5.9499999999999997E-2</v>
       </c>
-      <c r="K9" s="1">
-        <f t="shared" si="4"/>
-        <v>142.85714285714286</v>
-      </c>
-      <c r="L9" s="1">
-        <f t="shared" si="5"/>
-        <v>133.06666666666669</v>
-      </c>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10">
@@ -3119,14 +3081,8 @@
         <f t="shared" si="3"/>
         <v>6.6500000000000004E-2</v>
       </c>
-      <c r="K10" s="1">
-        <f t="shared" si="4"/>
-        <v>152.85714285714289</v>
-      </c>
-      <c r="L10" s="1">
-        <f t="shared" si="5"/>
-        <v>133.06666666666669</v>
-      </c>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11">
@@ -3215,73 +3171,55 @@
     </row>
     <row r="22" spans="1:6" ht="18" x14ac:dyDescent="0.2">
       <c r="C22" s="2"/>
-      <c r="F22" s="5">
-        <v>1.71</v>
-      </c>
+      <c r="F22" s="5"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C23" s="3"/>
       <c r="D23" s="4"/>
       <c r="E23" s="3"/>
-      <c r="F23" s="2">
-        <v>2.84</v>
-      </c>
+      <c r="F23" s="2"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C24" s="3"/>
       <c r="D24" s="4"/>
       <c r="E24" s="3"/>
-      <c r="F24" s="2">
-        <v>3.8</v>
-      </c>
+      <c r="F24" s="2"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C25" s="3"/>
       <c r="D25" s="4"/>
       <c r="E25" s="3"/>
-      <c r="F25" s="2">
-        <v>4.63</v>
-      </c>
+      <c r="F25" s="2"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C26" s="3"/>
       <c r="D26" s="4"/>
       <c r="E26" s="3"/>
-      <c r="F26" s="2">
-        <v>5.36</v>
-      </c>
+      <c r="F26" s="2"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C27" s="3"/>
       <c r="D27" s="4"/>
       <c r="E27" s="3"/>
-      <c r="F27" s="2">
-        <v>6.01</v>
-      </c>
+      <c r="F27" s="2"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C28" s="3"/>
       <c r="D28" s="4"/>
       <c r="E28" s="3"/>
-      <c r="F28" s="2">
-        <v>6.6</v>
-      </c>
+      <c r="F28" s="2"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C29" s="3"/>
       <c r="D29" s="4"/>
       <c r="E29" s="3"/>
-      <c r="F29" s="2">
-        <v>7.14</v>
-      </c>
+      <c r="F29" s="2"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C30" s="3"/>
       <c r="D30" s="4"/>
       <c r="E30" s="3"/>
-      <c r="F30" s="2">
-        <v>7.64</v>
-      </c>
+      <c r="F30" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3291,10 +3229,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A2AD08B-6B15-7F40-8452-B8D5EB243B4E}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="11" max="11" width="12.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3316,8 +3257,23 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3341,8 +3297,23 @@
         <f>$B$15/$B$13*B2</f>
         <v>9.0449999999999999</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <f>AVERAGE(B2:B3)/1000</f>
+        <v>4.2500000000000003E-2</v>
+      </c>
+      <c r="K2" s="1">
+        <f>(F3-F2)/(B3/1000-B2/1000)</f>
+        <v>162</v>
+      </c>
+      <c r="L2" s="7">
+        <f>(G3-G2)/(B3/1000-B2/1000)</f>
+        <v>200.99999999999991</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3366,8 +3337,23 @@
         <f t="shared" ref="G3:G10" si="1">$B$15/$B$13*B3</f>
         <v>8.0400000000000009</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <f t="shared" ref="J3:J9" si="2">AVERAGE(B3:B4)/1000</f>
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="K3" s="1">
+        <f t="shared" ref="K3:K9" si="3">(F4-F3)/(B4/1000-B3/1000)</f>
+        <v>146.00000000000017</v>
+      </c>
+      <c r="L3" s="7">
+        <f t="shared" ref="L3:L9" si="4">(G4-G3)/(B4/1000-B3/1000)</f>
+        <v>201.00000000000026</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3391,8 +3377,23 @@
         <f t="shared" si="1"/>
         <v>7.0350000000000001</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I4">
+        <v>3</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="2"/>
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="K4" s="1">
+        <f t="shared" si="3"/>
+        <v>146.66666666666654</v>
+      </c>
+      <c r="L4" s="7">
+        <f t="shared" si="4"/>
+        <v>200.9999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3416,8 +3417,23 @@
         <f t="shared" si="1"/>
         <v>6.03</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="2"/>
+        <v>2.75E-2</v>
+      </c>
+      <c r="K5" s="1">
+        <f t="shared" si="3"/>
+        <v>132.00000000000009</v>
+      </c>
+      <c r="L5" s="7">
+        <f t="shared" si="4"/>
+        <v>201.00000000000009</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3441,8 +3457,23 @@
         <f t="shared" si="1"/>
         <v>5.0250000000000004</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="2"/>
+        <v>2.2499999999999999E-2</v>
+      </c>
+      <c r="K6" s="1">
+        <f t="shared" si="3"/>
+        <v>156.00000000000003</v>
+      </c>
+      <c r="L6" s="7">
+        <f t="shared" si="4"/>
+        <v>200.99999999999994</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3466,8 +3497,23 @@
         <f t="shared" si="1"/>
         <v>4.0200000000000005</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I7">
+        <v>6</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="2"/>
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="K7" s="1">
+        <f t="shared" si="3"/>
+        <v>155.33333333333334</v>
+      </c>
+      <c r="L7" s="7">
+        <f t="shared" si="4"/>
+        <v>201.00000000000003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3491,8 +3537,23 @@
         <f t="shared" si="1"/>
         <v>3.0150000000000001</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I8">
+        <v>7</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="2"/>
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="K8" s="1">
+        <f t="shared" si="3"/>
+        <v>139.33333333333329</v>
+      </c>
+      <c r="L8" s="7">
+        <f t="shared" si="4"/>
+        <v>201</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3516,8 +3577,23 @@
         <f t="shared" si="1"/>
         <v>2.0100000000000002</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I9">
+        <v>8</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="2"/>
+        <v>7.4999999999999997E-3</v>
+      </c>
+      <c r="K9" s="1">
+        <f t="shared" si="3"/>
+        <v>140</v>
+      </c>
+      <c r="L9" s="7">
+        <f t="shared" si="4"/>
+        <v>201.00000000000003</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3542,11 +3618,11 @@
         <v>1.0050000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -3557,7 +3633,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -3568,7 +3644,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>9</v>
       </c>

--- a/lab2/31.xlsx
+++ b/lab2/31.xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/magdalenasmietana/Documents/Fizyka/Fizyka-Lab/lab2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dkomeza/Desktop/Fizyka-Lab/lab2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AE37496-DEDA-D149-8912-F58B65D92A22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2586A778-F0CD-AE45-900D-D1E6E344BBD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{9BA97022-0ECA-A347-BDBE-540DC07422D8}"/>
+    <workbookView xWindow="-8960" yWindow="-28800" windowWidth="51200" windowHeight="28800" xr2:uid="{9BA97022-0ECA-A347-BDBE-540DC07422D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Cylindryczny" sheetId="1" r:id="rId1"/>
     <sheet name="Płaski" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="pomiary_elektrostatyka" localSheetId="0">Cylindryczny!$S$3:$V$12</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -35,8 +38,23 @@
 </workbook>
 </file>
 
+<file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
+<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
+  <connection id="1" xr16:uid="{F15ABCC2-E4F9-5246-9426-D871F5559931}" name="pomiary_elektrostatyka" type="6" refreshedVersion="8" background="1" saveData="1">
+    <textPr fileType="mac" sourceFile="/Users/dkomeza/Downloads/pomiary_elektrostatyka.csv" tab="0" comma="1">
+      <textFields count="4">
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+      </textFields>
+    </textPr>
+  </connection>
+</connections>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="27">
   <si>
     <t>L.p.</t>
   </si>
@@ -97,13 +115,34 @@
   <si>
     <t>u( E ) [V/m]</t>
   </si>
+  <si>
+    <t>no.</t>
+  </si>
+  <si>
+    <t>x[mm]</t>
+  </si>
+  <si>
+    <t>y[mm]</t>
+  </si>
+  <si>
+    <t>voltage[V]</t>
+  </si>
+  <si>
+    <t>r* [m]</t>
+  </si>
+  <si>
+    <t>Edo≈õw [V/m]</t>
+  </si>
+  <si>
+    <t>Eteor [V/m]</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -175,7 +214,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -489,34 +528,34 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>1.524030147599758</c:v>
+                  <c:v>0.49024330657995224</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.8360742846310911</c:v>
+                  <c:v>1.0211432213122873</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.9879679442943261</c:v>
+                  <c:v>1.6000579914856792</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.0145888313429481</c:v>
+                  <c:v>2.2365440256890485</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.9405317310471943</c:v>
+                  <c:v>2.9433292610197381</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6.783791481549593</c:v>
+                  <c:v>3.7378931412830019</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7.5579317324709256</c:v>
+                  <c:v>4.6451723141632009</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8.2734301155978525</c:v>
+                  <c:v>5.7025169851942943</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>8.9385487870524329</c:v>
+                  <c:v>6.9696015006918257</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>9.5599181221975797</c:v>
+                  <c:v>8.5507535639998711</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -569,7 +608,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US"/>
-                  <a:t>Odległość od nakładki naładowanej potencjałem U</a:t>
+                  <a:t>Odległość od nakładki ujemnej</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -803,6 +842,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -810,7 +850,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -846,6 +885,615 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Natężenie doświadczalne a</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> teoretyczne</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Cylindryczny!$K$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>E_dośw [V/m]</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Cylindryczny!$M$2:$M$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>30.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>37.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>44.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>51.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>58.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>65.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>72.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>79.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>86.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Cylindryczny!$K$2:$K$9</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>52.380952380952387</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>63.3333333333333</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>72.380952380952408</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>74.761904761904773</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>82.857142857142861</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>83.333333333333357</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>114.76190476190469</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>144.76190476190482</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C4EA-1349-A23D-9423DA72268A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Cylindryczny!$L$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>E_teor [V/m]</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Cylindryczny!$M$2:$M$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>30.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>37.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>44.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>51.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>58.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>65.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>72.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>79.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>86.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Cylindryczny!$L$2:$L$9</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>75.799452443515847</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>82.645854599704393</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>90.851825978398438</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>100.86698789727701</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>113.3637828580016</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>129.39502487832505</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>150.70714662299034</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>180.42404877400253</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-C4EA-1349-A23D-9423DA72268A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="279359744"/>
+        <c:axId val="279359296"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="279359744"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Położenie między okładkami [mm]</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="279359296"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="279359296"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Natężenie pola [V/m]</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="279359744"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1192,6 +1840,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1199,7 +1848,609 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Natężenie doświadczalne a</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> teoretyczne</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Płaski!$K$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>E_dośw [V/m]</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Płaski!$N$2:$N$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>42.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>37.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>32.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>27.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>22.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Płaski!$K$2:$K$9</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>162</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>146.00000000000017</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>146.66666666666654</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>132.00000000000009</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>156.00000000000003</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>155.33333333333334</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>139.33333333333329</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>140</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3741-0742-9C36-0A8133A01F6E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Płaski!$L$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>E_teor [V/m]</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Płaski!$N$2:$N$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>42.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>37.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>32.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>27.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>22.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Płaski!$L$2:$L$9</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>200.99999999999991</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>201.00000000000026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>200.9999999999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>201.00000000000009</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>200.99999999999994</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>201.00000000000003</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>201</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>201.00000000000003</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-3741-0742-9C36-0A8133A01F6E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="279359744"/>
+        <c:axId val="279359296"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="279359744"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Położenie między okładkami [mm]</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="279359296"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="279359296"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Natężenie pola [V/m]</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="279359744"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1314,6 +2565,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
@@ -2346,20 +3677,1052 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>158750</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>562610</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>179070</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>514350</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>808990</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>107950</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2379,6 +4742,44 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>10160</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>214328</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>89</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B7F6C6F-210E-6644-ABE1-22075E9FC54D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2425,13 +4826,53 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>789963</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>125601</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>258660</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>95774</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{426DABF7-F014-82B8-5775-ED97803E5499}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
+<file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="pomiary_elektrostatyka" connectionId="1" xr16:uid="{97C89E28-DF94-4D4B-BE61-9D005CDCE742}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2469,7 +4910,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2575,7 +5016,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2717,7 +5158,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2725,16 +5166,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32A40C7D-DDDA-FA41-8140-030802D7CD28}">
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:W30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="6" max="7" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.1640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2769,7 +5214,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2791,8 +5236,12 @@
         <v>1.3</v>
       </c>
       <c r="G2" s="1">
-        <f>($B$15/LN($B$17/$B$16))*LN((B2 / 1000 + $B$16)/$B$16)</f>
-        <v>1.524030147599758</v>
+        <f>$B$15*(LN($B$17/($B$17-B2 / 1000)) / LN($B$17/$B$16))</f>
+        <v>0.49024330657995224</v>
+      </c>
+      <c r="H2">
+        <f>$B$16 + B2/1000</f>
+        <v>2.7E-2</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -2801,10 +5250,20 @@
         <f>AVERAGE(B2:B3) / 1000</f>
         <v>1.0500000000000001E-2</v>
       </c>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
+      <c r="K2" s="1">
+        <f>(F3-F2)/((B3-B2)/1000)</f>
+        <v>52.380952380952387</v>
+      </c>
+      <c r="L2" s="1">
+        <f>$B$15 / (($B$17 - J2) * LN($B$17/$B$16))</f>
+        <v>75.799452443515847</v>
+      </c>
+      <c r="M2">
+        <f>(J2) * 1000 + $B$16 * 1000</f>
+        <v>30.5</v>
+      </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2826,20 +5285,46 @@
         <v>1.6666666666666667</v>
       </c>
       <c r="G3" s="1">
-        <f t="shared" ref="G3:G11" si="2">($B$15/LN($B$17/$B$16))*LN((B3 / 1000 + $B$16)/$B$16)</f>
-        <v>2.8360742846310911</v>
+        <f t="shared" ref="G3:G11" si="2">$B$15*(LN($B$17/($B$17-B3 / 1000)) / LN($B$17/$B$16))</f>
+        <v>1.0211432213122873</v>
+      </c>
+      <c r="H3">
+        <f t="shared" ref="H3:H11" si="3">$B$16 + B3/1000</f>
+        <v>3.4000000000000002E-2</v>
       </c>
       <c r="I3">
         <v>2</v>
       </c>
       <c r="J3">
-        <f t="shared" ref="J3:J10" si="3">AVERAGE(B3:B4) / 1000</f>
+        <f t="shared" ref="J3:J10" si="4">AVERAGE(B3:B4) / 1000</f>
         <v>1.7500000000000002E-2</v>
       </c>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
+      <c r="K3" s="1">
+        <f t="shared" ref="K3:K10" si="5">(F4-F3)/((B4-B3)/1000)</f>
+        <v>63.3333333333333</v>
+      </c>
+      <c r="L3" s="1">
+        <f t="shared" ref="L3:L10" si="6">$B$15 / (($B$17 - J3) * LN($B$17/$B$16))</f>
+        <v>82.645854599704393</v>
+      </c>
+      <c r="M3">
+        <f t="shared" ref="M3:M10" si="7">(J3) * 1000 + $B$16 * 1000</f>
+        <v>37.5</v>
+      </c>
+      <c r="S3" t="s">
+        <v>0</v>
+      </c>
+      <c r="T3" t="s">
+        <v>24</v>
+      </c>
+      <c r="U3" t="s">
+        <v>25</v>
+      </c>
+      <c r="V3" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2862,19 +5347,49 @@
       </c>
       <c r="G4" s="1">
         <f t="shared" si="2"/>
-        <v>3.9879679442943261</v>
+        <v>1.6000579914856792</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="3"/>
+        <v>4.1000000000000002E-2</v>
       </c>
       <c r="I4">
         <v>3</v>
       </c>
       <c r="J4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.4500000000000001E-2</v>
       </c>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
+      <c r="K4" s="1">
+        <f t="shared" si="5"/>
+        <v>72.380952380952408</v>
+      </c>
+      <c r="L4" s="1">
+        <f t="shared" si="6"/>
+        <v>90.851825978398438</v>
+      </c>
+      <c r="M4">
+        <f t="shared" si="7"/>
+        <v>44.5</v>
+      </c>
+      <c r="S4">
+        <v>1</v>
+      </c>
+      <c r="T4">
+        <v>5.0500000000000003E-2</v>
+      </c>
+      <c r="U4">
+        <v>190</v>
+      </c>
+      <c r="V4">
+        <v>191.03</v>
+      </c>
+      <c r="W4">
+        <f>T4*1000</f>
+        <v>50.5</v>
+      </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2897,19 +5412,49 @@
       </c>
       <c r="G5" s="1">
         <f t="shared" si="2"/>
-        <v>5.0145888313429481</v>
+        <v>2.2365440256890485</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="3"/>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="I5">
         <v>4</v>
       </c>
       <c r="J5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.15E-2</v>
       </c>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
+      <c r="K5" s="1">
+        <f t="shared" si="5"/>
+        <v>74.761904761904773</v>
+      </c>
+      <c r="L5" s="1">
+        <f t="shared" si="6"/>
+        <v>100.86698789727701</v>
+      </c>
+      <c r="M5">
+        <f t="shared" si="7"/>
+        <v>51.5</v>
+      </c>
+      <c r="S5">
+        <v>2</v>
+      </c>
+      <c r="T5">
+        <v>5.7500000000000002E-2</v>
+      </c>
+      <c r="U5">
+        <v>144.29</v>
+      </c>
+      <c r="V5">
+        <v>167.76</v>
+      </c>
+      <c r="W5">
+        <f t="shared" ref="W5:W12" si="8">T5*1000</f>
+        <v>57.5</v>
+      </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2932,19 +5477,49 @@
       </c>
       <c r="G6" s="1">
         <f t="shared" si="2"/>
-        <v>5.9405317310471943</v>
+        <v>2.9433292610197381</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="3"/>
+        <v>5.5000000000000007E-2</v>
       </c>
       <c r="I6">
         <v>5</v>
       </c>
       <c r="J6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.85E-2</v>
       </c>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
+      <c r="K6" s="1">
+        <f t="shared" si="5"/>
+        <v>82.857142857142861</v>
+      </c>
+      <c r="L6" s="1">
+        <f t="shared" si="6"/>
+        <v>113.3637828580016</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="7"/>
+        <v>58.5</v>
+      </c>
+      <c r="S6">
+        <v>3</v>
+      </c>
+      <c r="T6">
+        <v>6.4500000000000002E-2</v>
+      </c>
+      <c r="U6">
+        <v>115.71</v>
+      </c>
+      <c r="V6">
+        <v>149.58000000000001</v>
+      </c>
+      <c r="W6">
+        <f t="shared" si="8"/>
+        <v>64.5</v>
+      </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2967,19 +5542,49 @@
       </c>
       <c r="G7" s="1">
         <f t="shared" si="2"/>
-        <v>6.783791481549593</v>
+        <v>3.7378931412830019</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="3"/>
+        <v>6.2E-2</v>
       </c>
       <c r="I7">
         <v>6</v>
       </c>
       <c r="J7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.5499999999999999E-2</v>
       </c>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
+      <c r="K7" s="1">
+        <f t="shared" si="5"/>
+        <v>83.333333333333357</v>
+      </c>
+      <c r="L7" s="1">
+        <f t="shared" si="6"/>
+        <v>129.39502487832505</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="7"/>
+        <v>65.5</v>
+      </c>
+      <c r="S7">
+        <v>4</v>
+      </c>
+      <c r="T7">
+        <v>7.1499999999999994E-2</v>
+      </c>
+      <c r="U7">
+        <v>82.86</v>
+      </c>
+      <c r="V7">
+        <v>134.91999999999999</v>
+      </c>
+      <c r="W7">
+        <f t="shared" si="8"/>
+        <v>71.5</v>
+      </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3002,19 +5607,49 @@
       </c>
       <c r="G8" s="1">
         <f t="shared" si="2"/>
-        <v>7.5579317324709256</v>
+        <v>4.6451723141632009</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="3"/>
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="I8">
         <v>7</v>
       </c>
       <c r="J8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.2499999999999998E-2</v>
       </c>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
+      <c r="K8" s="1">
+        <f t="shared" si="5"/>
+        <v>114.76190476190469</v>
+      </c>
+      <c r="L8" s="1">
+        <f t="shared" si="6"/>
+        <v>150.70714662299034</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="7"/>
+        <v>72.5</v>
+      </c>
+      <c r="S8">
+        <v>5</v>
+      </c>
+      <c r="T8">
+        <v>7.85E-2</v>
+      </c>
+      <c r="U8">
+        <v>82.86</v>
+      </c>
+      <c r="V8">
+        <v>122.9</v>
+      </c>
+      <c r="W8">
+        <f t="shared" si="8"/>
+        <v>78.5</v>
+      </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3037,19 +5672,49 @@
       </c>
       <c r="G9" s="1">
         <f t="shared" si="2"/>
-        <v>8.2734301155978525</v>
+        <v>5.7025169851942943</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="3"/>
+        <v>7.5999999999999998E-2</v>
       </c>
       <c r="I9">
         <v>8</v>
       </c>
       <c r="J9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.9499999999999997E-2</v>
       </c>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
+      <c r="K9" s="1">
+        <f t="shared" si="5"/>
+        <v>144.76190476190482</v>
+      </c>
+      <c r="L9" s="1">
+        <f t="shared" si="6"/>
+        <v>180.42404877400253</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="7"/>
+        <v>79.5</v>
+      </c>
+      <c r="S9">
+        <v>6</v>
+      </c>
+      <c r="T9">
+        <v>8.5500000000000007E-2</v>
+      </c>
+      <c r="U9">
+        <v>74.290000000000006</v>
+      </c>
+      <c r="V9">
+        <v>112.82</v>
+      </c>
+      <c r="W9">
+        <f t="shared" si="8"/>
+        <v>85.5</v>
+      </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3072,19 +5737,49 @@
       </c>
       <c r="G10" s="1">
         <f t="shared" si="2"/>
-        <v>8.9385487870524329</v>
+        <v>6.9696015006918257</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="3"/>
+        <v>8.3000000000000004E-2</v>
       </c>
       <c r="I10">
         <v>9</v>
       </c>
       <c r="J10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6.6500000000000004E-2</v>
       </c>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
+      <c r="K10" s="1">
+        <f t="shared" si="5"/>
+        <v>190</v>
+      </c>
+      <c r="L10" s="1">
+        <f t="shared" si="6"/>
+        <v>224.73872742024881</v>
+      </c>
+      <c r="M10">
+        <f t="shared" si="7"/>
+        <v>86.5</v>
+      </c>
+      <c r="S10">
+        <v>7</v>
+      </c>
+      <c r="T10">
+        <v>9.2499999999999999E-2</v>
+      </c>
+      <c r="U10">
+        <v>72.86</v>
+      </c>
+      <c r="V10">
+        <v>104.29</v>
+      </c>
+      <c r="W10">
+        <f t="shared" si="8"/>
+        <v>92.5</v>
+      </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -3107,10 +5802,48 @@
       </c>
       <c r="G11" s="1">
         <f t="shared" si="2"/>
-        <v>9.5599181221975797</v>
+        <v>8.5507535639998711</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="3"/>
+        <v>9.0000000000000011E-2</v>
+      </c>
+      <c r="S11">
+        <v>8</v>
+      </c>
+      <c r="T11">
+        <v>9.9500000000000005E-2</v>
+      </c>
+      <c r="U11">
+        <v>62.86</v>
+      </c>
+      <c r="V11">
+        <v>96.95</v>
+      </c>
+      <c r="W11">
+        <f t="shared" si="8"/>
+        <v>99.5</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="S12">
+        <v>9</v>
+      </c>
+      <c r="T12">
+        <v>0.1065</v>
+      </c>
+      <c r="U12">
+        <v>52.86</v>
+      </c>
+      <c r="V12">
+        <v>90.58</v>
+      </c>
+      <c r="W12">
+        <f t="shared" si="8"/>
+        <v>106.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -3121,7 +5854,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -3132,7 +5865,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>9</v>
       </c>
@@ -3143,12 +5876,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>15</v>
       </c>
       <c r="B16">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="C16" t="s">
         <v>17</v>
@@ -3160,7 +5893,7 @@
       </c>
       <c r="B17">
         <f>B16+B13 / 1000</f>
-        <v>0.11499999999999999</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="C17" t="s">
         <v>17</v>
@@ -3229,13 +5962,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A2AD08B-6B15-7F40-8452-B8D5EB243B4E}">
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:N40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="11" max="11" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3273,7 +6006,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3312,8 +6045,12 @@
         <f>(G3-G2)/(B3/1000-B2/1000)</f>
         <v>200.99999999999991</v>
       </c>
+      <c r="N2">
+        <f>J2*1000</f>
+        <v>42.5</v>
+      </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3352,8 +6089,12 @@
         <f t="shared" ref="L3:L9" si="4">(G4-G3)/(B4/1000-B3/1000)</f>
         <v>201.00000000000026</v>
       </c>
+      <c r="N3">
+        <f t="shared" ref="N3:N9" si="5">J3*1000</f>
+        <v>37.5</v>
+      </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3392,8 +6133,12 @@
         <f t="shared" si="4"/>
         <v>200.9999999999998</v>
       </c>
+      <c r="N4">
+        <f t="shared" si="5"/>
+        <v>32.5</v>
+      </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3432,8 +6177,12 @@
         <f t="shared" si="4"/>
         <v>201.00000000000009</v>
       </c>
+      <c r="N5">
+        <f t="shared" si="5"/>
+        <v>27.5</v>
+      </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3472,8 +6221,12 @@
         <f t="shared" si="4"/>
         <v>200.99999999999994</v>
       </c>
+      <c r="N6">
+        <f t="shared" si="5"/>
+        <v>22.5</v>
+      </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3512,8 +6265,12 @@
         <f t="shared" si="4"/>
         <v>201.00000000000003</v>
       </c>
+      <c r="N7">
+        <f t="shared" si="5"/>
+        <v>17.5</v>
+      </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3552,8 +6309,12 @@
         <f t="shared" si="4"/>
         <v>201</v>
       </c>
+      <c r="N8">
+        <f t="shared" si="5"/>
+        <v>12.5</v>
+      </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3592,8 +6353,12 @@
         <f t="shared" si="4"/>
         <v>201.00000000000003</v>
       </c>
+      <c r="N9">
+        <f t="shared" si="5"/>
+        <v>7.5</v>
+      </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3618,11 +6383,11 @@
         <v>1.0050000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -3633,7 +6398,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -3644,7 +6409,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>9</v>
       </c>
@@ -3653,6 +6418,20 @@
       </c>
       <c r="C15" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>20</v>
+      </c>
+      <c r="B40" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" t="s">
+        <v>22</v>
+      </c>
+      <c r="D40" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
